--- a/docs/hka/Bestellung 2.xlsx
+++ b/docs/hka/Bestellung 2.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jax\Coding\sdr-analog-frontend\docs\hka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC98CA23-8684-489D-8BAE-55CC90839DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E795E0A-38A9-4BE3-BC14-F2D74C240159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
-    <sheet name="Tabelle3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Artikel.-Nr.</t>
   </si>
@@ -149,12 +147,6 @@
     <t>Dickfilmwiderstände - SMD 1/10W 33.2Kohms 1% Commercial Use</t>
   </si>
   <si>
-    <t>KAM05AR71H102JH</t>
-  </si>
-  <si>
-    <t>Kondensator aus mehreren Keramikschichten MLCC - SMD/SMT 50V 1000pF X7R 0402 5% AEC-Q200</t>
-  </si>
-  <si>
     <t>LQW15CAR64J00D</t>
   </si>
   <si>
@@ -165,33 +157,6 @@
   </si>
   <si>
     <t>HF-Induktivitäten – SMD IND 27.00 nH 0.490 A 190.00 mOhm</t>
-  </si>
-  <si>
-    <t>TSW-101-07-G-S</t>
-  </si>
-  <si>
-    <t>Sockel &amp; Kabelgehäuse 2.54 CLASSIC PCB HDR STRIP</t>
-  </si>
-  <si>
-    <t>TSW-103-07-G-S</t>
-  </si>
-  <si>
-    <t>Sockel &amp; Kabelgehäuse Through-Hole .025" Sq Post Header</t>
-  </si>
-  <si>
-    <t>TSW-106-07-G-S</t>
-  </si>
-  <si>
-    <t>Sockel &amp; Kabelgehäuse 2.54MM CLASSIC PCB HDR STRIP</t>
-  </si>
-  <si>
-    <t>https://www.mouser.de/de/ProductDetail/Samtec/TSW-106-07-G-S?qs=NxGO64s6WXhoKs3GtKmiLA%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.mouser.de/de/ProductDetail/Samtec/TSW-103-07-G-S?qs=iT52DjcXudtntd1jApTIAw%3D%3D</t>
-  </si>
-  <si>
-    <t>https://www.mouser.de/de/ProductDetail/Samtec/TSW-101-07-G-S?qs=hzq9O0YpnZscfPe5oPvABA%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1062,7 @@
     </row>
     <row r="23" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>33</v>
@@ -1110,7 +1075,7 @@
       </c>
       <c r="E23" s="30">
         <f t="shared" ref="E23:E50" si="0">A23*D23</f>
-        <v>0.17199999999999999</v>
+        <v>0.42999999999999994</v>
       </c>
       <c r="F23" s="31" t="s">
         <v>34</v>
@@ -1118,7 +1083,7 @@
     </row>
     <row r="24" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>35</v>
@@ -1131,13 +1096,13 @@
       </c>
       <c r="E24" s="30">
         <f t="shared" si="0"/>
-        <v>0.439</v>
+        <v>0.878</v>
       </c>
       <c r="F24" s="31"/>
     </row>
     <row r="25" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>38</v>
@@ -1146,17 +1111,17 @@
         <v>39</v>
       </c>
       <c r="D25" s="37">
-        <v>0.12</v>
+        <v>0.35299999999999998</v>
       </c>
       <c r="E25" s="30">
-        <f t="shared" ref="E25:E32" si="1">A25*D25</f>
-        <v>0.72</v>
+        <f t="shared" si="0"/>
+        <v>1.7649999999999999</v>
       </c>
       <c r="F25" s="31"/>
     </row>
     <row r="26" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>40</v>
@@ -1165,95 +1130,53 @@
         <v>41</v>
       </c>
       <c r="D26" s="37">
-        <v>0.35299999999999998</v>
+        <v>0.18099999999999999</v>
       </c>
       <c r="E26" s="30">
-        <f t="shared" ref="E26" si="2">A26*D26</f>
-        <v>0.70599999999999996</v>
+        <f t="shared" si="0"/>
+        <v>0.90500000000000003</v>
       </c>
       <c r="F26" s="31"/>
     </row>
     <row r="27" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="14">
-        <v>2</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="D27" s="37">
-        <v>0.18099999999999999</v>
-      </c>
       <c r="E27" s="30">
-        <f t="shared" si="1"/>
-        <v>0.36199999999999999</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F27" s="31"/>
     </row>
     <row r="28" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="14">
-        <v>1</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="35">
-        <v>0.52500000000000002</v>
-      </c>
+      <c r="A28" s="14"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="35"/>
       <c r="E28" s="30">
-        <f t="shared" si="1"/>
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="F28" s="31" t="s">
-        <v>50</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="31"/>
     </row>
     <row r="29" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="14">
-        <v>3</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="35">
-        <v>0.28399999999999997</v>
-      </c>
+      <c r="A29" s="14"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="35"/>
       <c r="E29" s="30">
-        <f t="shared" si="1"/>
-        <v>0.85199999999999987</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>51</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="31"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="14">
-        <v>3</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="35">
-        <v>0.18099999999999999</v>
-      </c>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="35"/>
       <c r="E30" s="30">
-        <f t="shared" si="1"/>
-        <v>0.54299999999999993</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>52</v>
-      </c>
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="14"/>
@@ -1261,7 +1184,7 @@
       <c r="C31" s="15"/>
       <c r="D31" s="20"/>
       <c r="E31" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F31" s="31"/>
@@ -1272,7 +1195,7 @@
       <c r="C32" s="15"/>
       <c r="D32" s="19"/>
       <c r="E32" s="30">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E32" si="1">A32*D32</f>
         <v>0</v>
       </c>
       <c r="F32" s="31"/>
@@ -1283,7 +1206,7 @@
       <c r="C33" s="15"/>
       <c r="D33" s="19"/>
       <c r="E33" s="30">
-        <f t="shared" ref="E33:E35" si="3">A33*D33</f>
+        <f t="shared" ref="E33:E35" si="2">A33*D33</f>
         <v>0</v>
       </c>
       <c r="F33" s="31"/>
@@ -1294,7 +1217,7 @@
       <c r="C34" s="15"/>
       <c r="D34" s="20"/>
       <c r="E34" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F34" s="31"/>
@@ -1305,7 +1228,7 @@
       <c r="C35" s="15"/>
       <c r="D35" s="19"/>
       <c r="E35" s="30">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F35" s="31"/>
@@ -1316,7 +1239,7 @@
       <c r="C36" s="15"/>
       <c r="D36" s="19"/>
       <c r="E36" s="30">
-        <f t="shared" ref="E36:E41" si="4">A36*D36</f>
+        <f t="shared" ref="E36:E41" si="3">A36*D36</f>
         <v>0</v>
       </c>
       <c r="F36" s="31"/>
@@ -1327,7 +1250,7 @@
       <c r="C37" s="15"/>
       <c r="D37" s="20"/>
       <c r="E37" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F37" s="31"/>
@@ -1338,7 +1261,7 @@
       <c r="C38" s="15"/>
       <c r="D38" s="19"/>
       <c r="E38" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F38" s="31"/>
@@ -1349,7 +1272,7 @@
       <c r="C39" s="15"/>
       <c r="D39" s="19"/>
       <c r="E39" s="30">
-        <f t="shared" ref="E39" si="5">A39*D39</f>
+        <f t="shared" ref="E39" si="4">A39*D39</f>
         <v>0</v>
       </c>
       <c r="F39" s="31"/>
@@ -1360,7 +1283,7 @@
       <c r="C40" s="15"/>
       <c r="D40" s="20"/>
       <c r="E40" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F40" s="31"/>
@@ -1371,7 +1294,7 @@
       <c r="C41" s="15"/>
       <c r="D41" s="19"/>
       <c r="E41" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F41" s="31"/>
@@ -1382,7 +1305,7 @@
       <c r="C42" s="15"/>
       <c r="D42" s="19"/>
       <c r="E42" s="30">
-        <f t="shared" ref="E42:E44" si="6">A42*D42</f>
+        <f t="shared" ref="E42:E44" si="5">A42*D42</f>
         <v>0</v>
       </c>
       <c r="F42" s="31"/>
@@ -1393,7 +1316,7 @@
       <c r="C43" s="15"/>
       <c r="D43" s="20"/>
       <c r="E43" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F43" s="31"/>
@@ -1404,7 +1327,7 @@
       <c r="C44" s="15"/>
       <c r="D44" s="19"/>
       <c r="E44" s="30">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F44" s="31"/>
@@ -1484,7 +1407,7 @@
       </c>
       <c r="E52" s="24">
         <f>SUM(E23:E49)</f>
-        <v>4.319</v>
+        <v>3.9779999999999998</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -1493,7 +1416,7 @@
       </c>
       <c r="E53" s="26">
         <f>E52*0.19</f>
-        <v>0.82060999999999995</v>
+        <v>0.75581999999999994</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -1502,7 +1425,7 @@
       </c>
       <c r="E54" s="28">
         <f>E52+E53</f>
-        <v>5.1396100000000002</v>
+        <v>4.7338199999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1512,34 +1435,11 @@
     <hyperlink ref="C5" r:id="rId2" display="https://www.mouser.de/contact/" xr:uid="{47CAD5B4-9045-4FF3-B7BA-0A15C4EC32AD}"/>
     <hyperlink ref="C8" r:id="rId3" display="mailto:muenchen%40mouser.com" xr:uid="{18A9A27D-B7AE-4470-A4F3-58A589B5CCA4}"/>
     <hyperlink ref="B24" r:id="rId4" display="https://www.mouser.de/de/ProductDetail/Diodes-Incorporated/DMP3068L-13?qs=BvpHGKeVh3oYv%2Fo7o2xLFg%3D%3D" xr:uid="{29E187AD-FB00-4227-A2D9-F4DB841F246D}"/>
-    <hyperlink ref="B25" r:id="rId5" display="https://www.mouser.de/de/ProductDetail/KYOCERA-AVX/KAM05AR71H102JH?qs=sGAEpiMZZMsh%252B1woXyUXj17cMikWvs6%2FqOVrMntdmkU%3D" xr:uid="{52382EBE-7A49-4DB7-B715-B042C3E89203}"/>
-    <hyperlink ref="B26" r:id="rId6" display="https://www.mouser.de/de/ProductDetail/Murata-Electronics/LQW15CAR64J00D?qs=Ih85XBhZ45kF6EpVY%252BTZWA%3D%3D" xr:uid="{906C09CA-63BD-4C5A-AED5-823CBA7AF20B}"/>
-    <hyperlink ref="B27" r:id="rId7" display="https://www.mouser.de/de/ProductDetail/ABRACON/AISC-0603-R027J-T?qs=nwAb7ZGSLg4FkdvwVP4kEA%3D%3D" xr:uid="{FB04E394-CF9B-4975-B3A5-0D15E1CA379A}"/>
+    <hyperlink ref="B25" r:id="rId5" display="https://www.mouser.de/de/ProductDetail/Murata-Electronics/LQW15CAR64J00D?qs=Ih85XBhZ45kF6EpVY%252BTZWA%3D%3D" xr:uid="{906C09CA-63BD-4C5A-AED5-823CBA7AF20B}"/>
+    <hyperlink ref="B26" r:id="rId6" display="https://www.mouser.de/de/ProductDetail/ABRACON/AISC-0603-R027J-T?qs=nwAb7ZGSLg4FkdvwVP4kEA%3D%3D" xr:uid="{FB04E394-CF9B-4975-B3A5-0D15E1CA379A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="60" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId8"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
+  <pageSetup paperSize="9" scale="60" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId7"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>